--- a/configs/Unit.xlsx
+++ b/configs/Unit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95697546-6C28-4585-AC2C-BB15E65F805C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BADB6C-5FCF-4740-992A-4FEFE5EE491F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="8220" yWindow="3680" windowWidth="28800" windowHeight="15370" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -74,15 +74,6 @@
     <t>🧝</t>
   </si>
   <si>
-    <t>maxhp:52;maxmp:0</t>
-  </si>
-  <si>
-    <t>maxhp:29;maxmp:30</t>
-  </si>
-  <si>
-    <t>maxhp:36;maxmp:19</t>
-  </si>
-  <si>
     <t>Enum:UnitId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -168,6 +159,15 @@
   </si>
   <si>
     <t>🧕</t>
+  </si>
+  <si>
+    <t>maxhp:52;maxmp:0;xdmg:1,4;str:20;int:5;spi:5;vit:20</t>
+  </si>
+  <si>
+    <t>maxhp:29;maxmp:30;xdmg:1,3;str:10;int:20;spi:10;vit:10</t>
+  </si>
+  <si>
+    <t>maxhp:36;maxmp:19;xdmg:1,3;str:10;int:10;spi:15;vit:15</t>
   </si>
 </sst>
 </file>
@@ -580,7 +580,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -594,13 +594,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>8</v>
@@ -609,32 +609,32 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -642,16 +642,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -659,16 +659,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -676,63 +676,63 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/configs/Unit.xlsx
+++ b/configs/Unit.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yatyr\workspace\gvbasic-mir-remaster\configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BADB6C-5FCF-4740-992A-4FEFE5EE491F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F115FD0F-71A6-4C4D-B46B-0AD7468FB97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8220" yWindow="3680" windowWidth="28800" windowHeight="15370" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
+    <workbookView xWindow="2460" yWindow="2460" windowWidth="30825" windowHeight="15345" xr2:uid="{BE06346D-0448-4393-8808-56E6116DD3E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="43">
   <si>
     <t>id</t>
   </si>
@@ -161,13 +161,13 @@
     <t>🧕</t>
   </si>
   <si>
-    <t>maxhp:52;maxmp:0;xdmg:1,4;str:20;int:5;spi:5;vit:20</t>
-  </si>
-  <si>
-    <t>maxhp:29;maxmp:30;xdmg:1,3;str:10;int:20;spi:10;vit:10</t>
-  </si>
-  <si>
-    <t>maxhp:36;maxmp:19;xdmg:1,3;str:10;int:10;spi:15;vit:15</t>
+    <t>maxhp:52;maxmp:0;xdmg:1,4;str:20;int:5;spi:5;vit:20;crit:5;critd:100;scrit:5;scritd:100</t>
+  </si>
+  <si>
+    <t>maxhp:29;maxmp:30;xdmg:1,3;str:10;int:20;spi:10;vit:10;crit:5;critd:100;scrit:5;scritd:100</t>
+  </si>
+  <si>
+    <t>maxhp:36;maxmp:19;xdmg:1,3;str:10;int:10;spi:15;vit:15;crit:5;critd:100;scrit:5;scritd:100</t>
   </si>
 </sst>
 </file>
@@ -561,18 +561,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7F59DC-7A1E-447A-A632-2A0549861B5B}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -592,7 +592,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -612,12 +612,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -637,7 +637,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -654,7 +654,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -671,7 +671,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -688,7 +688,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
@@ -699,7 +699,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
@@ -710,7 +710,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>35</v>
       </c>
@@ -721,7 +721,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>36</v>
       </c>

--- a/configs/Unit.xlsx
+++ b/configs/Unit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nef\workspace\gvbasic-mir-remaster\configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477D0A8E-47F1-4A47-8C65-02E67152D2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6754A12B-A051-4E31-97A3-80F279990BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="2070" windowWidth="30825" windowHeight="15345" xr2:uid="{8B8A063B-CFC4-4F06-BD5C-8A5A4B5A6380}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="339">
   <si>
     <t>id</t>
   </si>
@@ -1028,6 +1028,15 @@
   </si>
   <si>
     <t>woma</t>
+  </si>
+  <si>
+    <t>rift</t>
+  </si>
+  <si>
+    <t>秘境</t>
+  </si>
+  <si>
+    <t>🌀</t>
   </si>
 </sst>
 </file>
@@ -1898,7 +1907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D44C4F9-C313-4CB6-B781-2126B0F653E2}">
-  <dimension ref="A1:S84"/>
+  <dimension ref="A1:S85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="9.140625" style="1"/>
@@ -5945,6 +5954,20 @@
         <v>272</v>
       </c>
     </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>336</v>
+      </c>
+      <c r="B85" t="s">
+        <v>337</v>
+      </c>
+      <c r="C85" t="s">
+        <v>254</v>
+      </c>
+      <c r="G85" t="s">
+        <v>338</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
